--- a/VerveStacks_POL/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{092BB148-F113-4A66-A5DD-D6F5B9CA252B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DD92390-086B-473F-AF5F-52E53365B53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="353">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1200,7 +1200,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1348,8 +1348,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1441,6 +1448,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1655,7 +1667,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1675,8 +1687,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2068,6 +2081,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2087,8 +2101,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -2481,423 +2496,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -2905,32 +2593,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -2938,37 +2626,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -2980,120 +2668,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1000</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
+        <v>Trd_electricity export</v>
+      </c>
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>1000</v>
+      </c>
+      <c r="S28">
+        <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
         <v>19</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>1000</v>
-      </c>
-      <c r="S18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1000</v>
-      </c>
-      <c r="S19">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4639,25 +4662,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -4703,7 +4726,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -4748,7 +4771,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -4790,7 +4813,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -5895,7 +5918,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1E315A-3F71-4E62-9949-29CFD8D989E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D408F56-7620-494C-B212-9CC7C899E8AC}">
   <dimension ref="B9:M30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6648,7 +6671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1104DC3C-930F-4989-A175-4BC93E7912CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0956D1FA-355E-413B-B5EA-23F74F342DB0}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7770,7 +7793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D9BB4D-D8EE-49C0-86C1-8FD799F7E5A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789BE281-9B37-4BA3-9871-CE6591F10709}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
